--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142441</v>
       </c>
       <c r="B2" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142441</v>
       </c>
       <c r="B2" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,544 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130339833</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 60671, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>594110</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6427966</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130339825</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 60671, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>594100</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6427971</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130339870</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105987</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 62889, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593979</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6427811</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130339774</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 60671, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>594097</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6427967</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130339839</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 60671, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>594102</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6427961</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -1000,35 +1000,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130339870</v>
+        <v>130339774</v>
       </c>
       <c r="B5" t="n">
-        <v>105987</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1039,14 +1043,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 62889, Troserum, Sm</t>
+          <t>A 60671, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593979</v>
+        <v>594097</v>
       </c>
       <c r="R5" t="n">
-        <v>6427811</v>
+        <v>6427967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,39 +1110,35 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130339774</v>
+        <v>130339870</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>105987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1149,14 +1149,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 60671, Troserum, Sm</t>
+          <t>A 62889, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594097</v>
+        <v>593979</v>
       </c>
       <c r="R6" t="n">
-        <v>6427967</v>
+        <v>6427811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -1000,39 +1000,35 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130339774</v>
+        <v>130339870</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>105987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1043,14 +1039,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 60671, Troserum, Sm</t>
+          <t>A 62889, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594097</v>
+        <v>593979</v>
       </c>
       <c r="R5" t="n">
-        <v>6427967</v>
+        <v>6427811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,35 +1106,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130339870</v>
+        <v>130339774</v>
       </c>
       <c r="B6" t="n">
-        <v>105987</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1149,14 +1149,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 62889, Troserum, Sm</t>
+          <t>A 60671, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593979</v>
+        <v>594097</v>
       </c>
       <c r="R6" t="n">
-        <v>6427811</v>
+        <v>6427967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142441</v>
       </c>
       <c r="B2" t="n">
-        <v>93048</v>
+        <v>93051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130339833</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130339825</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>130339870</v>
       </c>
       <c r="B5" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130339774</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130339839</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142441</v>
       </c>
       <c r="B2" t="n">
-        <v>93051</v>
+        <v>93077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130339833</v>
       </c>
       <c r="B3" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130339825</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>130339870</v>
       </c>
       <c r="B5" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130339774</v>
       </c>
       <c r="B6" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130339839</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142441</v>
       </c>
       <c r="B2" t="n">
-        <v>93077</v>
+        <v>93078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130339833</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130339825</v>
       </c>
       <c r="B4" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>130339870</v>
       </c>
       <c r="B5" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130339774</v>
       </c>
       <c r="B6" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130339839</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>130339833</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130339825</v>
       </c>
       <c r="B4" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>130339870</v>
       </c>
       <c r="B5" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130339774</v>
       </c>
       <c r="B6" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130339839</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>130339833</v>
       </c>
       <c r="B3" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130339825</v>
       </c>
       <c r="B4" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>130339870</v>
       </c>
       <c r="B5" t="n">
-        <v>106018</v>
+        <v>106020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130339774</v>
       </c>
       <c r="B6" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130339839</v>
       </c>
       <c r="B7" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>130339833</v>
       </c>
       <c r="B3" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130339825</v>
       </c>
       <c r="B4" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>130339870</v>
       </c>
       <c r="B5" t="n">
-        <v>106020</v>
+        <v>106024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130339774</v>
       </c>
       <c r="B6" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130339839</v>
       </c>
       <c r="B7" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>130339833</v>
       </c>
       <c r="B3" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130339825</v>
       </c>
       <c r="B4" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>130339870</v>
       </c>
       <c r="B5" t="n">
-        <v>106024</v>
+        <v>106037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>130339774</v>
       </c>
       <c r="B6" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130339839</v>
       </c>
       <c r="B7" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>130339833</v>
       </c>
       <c r="B3" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130339825</v>
       </c>
       <c r="B4" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,35 +1000,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130339870</v>
+        <v>130339774</v>
       </c>
       <c r="B5" t="n">
-        <v>106037</v>
+        <v>98971</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1039,14 +1043,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 62889, Troserum, Sm</t>
+          <t>A 60671, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593979</v>
+        <v>594097</v>
       </c>
       <c r="R5" t="n">
-        <v>6427811</v>
+        <v>6427967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,39 +1110,35 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130339774</v>
+        <v>130339870</v>
       </c>
       <c r="B6" t="n">
-        <v>98970</v>
+        <v>106038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1149,14 +1149,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 60671, Troserum, Sm</t>
+          <t>A 62889, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594097</v>
+        <v>593979</v>
       </c>
       <c r="R6" t="n">
-        <v>6427967</v>
+        <v>6427811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
         <v>130339839</v>
       </c>
       <c r="B7" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>130339833</v>
       </c>
       <c r="B3" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130339825</v>
       </c>
       <c r="B4" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>130339774</v>
       </c>
       <c r="B5" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>130339870</v>
       </c>
       <c r="B6" t="n">
-        <v>106038</v>
+        <v>106041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130339839</v>
       </c>
       <c r="B7" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -1000,39 +1000,35 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130339774</v>
+        <v>130339870</v>
       </c>
       <c r="B5" t="n">
-        <v>98974</v>
+        <v>106041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1043,14 +1039,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 60671, Troserum, Sm</t>
+          <t>A 62889, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594097</v>
+        <v>593979</v>
       </c>
       <c r="R5" t="n">
-        <v>6427967</v>
+        <v>6427811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,35 +1106,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130339870</v>
+        <v>130339774</v>
       </c>
       <c r="B6" t="n">
-        <v>106041</v>
+        <v>98974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1149,14 +1149,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 62889, Troserum, Sm</t>
+          <t>A 60671, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593979</v>
+        <v>594097</v>
       </c>
       <c r="R6" t="n">
-        <v>6427811</v>
+        <v>6427967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 60671-2025 artfynd.xlsx
+++ b/artfynd/A 60671-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142441</v>
       </c>
       <c r="B2" t="n">
-        <v>93078</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130339833</v>
+        <v>130339774</v>
       </c>
       <c r="B3" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -827,14 +827,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 60671, Sm</t>
+          <t>A 60671, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594110</v>
+        <v>594097</v>
       </c>
       <c r="R3" t="n">
-        <v>6427966</v>
+        <v>6427967</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
         <v>130339825</v>
       </c>
       <c r="B4" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,35 +1000,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130339870</v>
+        <v>130339833</v>
       </c>
       <c r="B5" t="n">
-        <v>106041</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1039,14 +1043,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 62889, Troserum, Sm</t>
+          <t>A 60671, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593979</v>
+        <v>594110</v>
       </c>
       <c r="R5" t="n">
-        <v>6427811</v>
+        <v>6427966</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130339774</v>
+        <v>130339839</v>
       </c>
       <c r="B6" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,11 +1138,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594097</v>
+        <v>594102</v>
       </c>
       <c r="R6" t="n">
-        <v>6427967</v>
+        <v>6427961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,32 +1216,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130339839</v>
+        <v>130339870</v>
       </c>
       <c r="B7" t="n">
-        <v>98974</v>
+        <v>106243</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,14 +1255,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 60671, Troserum, Sm</t>
+          <t>A 62889, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594102</v>
+        <v>593979</v>
       </c>
       <c r="R7" t="n">
-        <v>6427961</v>
+        <v>6427811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
